--- a/model_info/det_gpt_pet.xlsx
+++ b/model_info/det_gpt_pet.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="6.6000000000000005" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.45</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.11918726434855466</v>
+        <v>0.4663732931912265</v>
       </c>
     </row>
     <row r="2">
@@ -589,7 +589,7 @@
         <v>1.0</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="6">
@@ -883,7 +883,7 @@
         <v>1.0</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="12">
@@ -1226,7 +1226,7 @@
         <v>1.0</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.9857831239020144</v>
+        <v>0.9928915619510073</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.7381396956501155</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.24946831773241573</v>
+        <v>0.6142078430767342</v>
       </c>
     </row>
     <row r="20">
@@ -1569,7 +1569,7 @@
         <v>0.6794231121910129</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.5761072261072262</v>
+        <v>0.7880536130536131</v>
       </c>
     </row>
     <row r="26">
@@ -1618,7 +1618,7 @@
         <v>0.41061349582177015</v>
       </c>
       <c r="O26" s="0" t="n">
-        <v>0.41725533596837944</v>
+        <v>0.5798851530141299</v>
       </c>
     </row>
     <row r="27">
@@ -1765,7 +1765,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>0.37777777777777777</v>
+        <v>0.6412698412698412</v>
       </c>
     </row>
     <row r="30">
@@ -1814,7 +1814,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6617647058823529</v>
       </c>
     </row>
     <row r="31">
@@ -1912,7 +1912,7 @@
         <v>1.0</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7029914529914529</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.7</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9464285714285714</v>
       </c>
     </row>
     <row r="34">
@@ -2108,7 +2108,7 @@
         <v>1.0</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.763265306122449</v>
+        <v>0.8306122448979592</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/det_gpt_pet.xlsx
+++ b/model_info/det_gpt_pet.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="6.6000000000000005" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.45</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.4663732931912265</v>
+        <v>0.09696590997848516</v>
       </c>
     </row>
     <row r="2">
@@ -589,7 +589,7 @@
         <v>1.0</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6296296296296295</v>
       </c>
     </row>
     <row r="6">
@@ -883,7 +883,7 @@
         <v>1.0</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -1226,7 +1226,7 @@
         <v>1.0</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.9928915619510073</v>
+        <v>0.9857831239020144</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.7381396956501155</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.6142078430767342</v>
+        <v>0.24421635314857543</v>
       </c>
     </row>
     <row r="20">
@@ -1569,7 +1569,7 @@
         <v>0.6794231121910129</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.7880536130536131</v>
+        <v>0.5761072261072262</v>
       </c>
     </row>
     <row r="26">
@@ -1618,7 +1618,7 @@
         <v>0.41061349582177015</v>
       </c>
       <c r="O26" s="0" t="n">
-        <v>0.5798851530141299</v>
+        <v>0.3098183332938866</v>
       </c>
     </row>
     <row r="27">
@@ -1765,7 +1765,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>0.6412698412698412</v>
+        <v>0.34179894179894177</v>
       </c>
     </row>
     <row r="30">
@@ -1814,7 +1814,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>0.6617647058823529</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="31">
@@ -1912,7 +1912,7 @@
         <v>1.0</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.7029914529914529</v>
+        <v>0.42735042735042733</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.7</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.8928571428571428</v>
       </c>
     </row>
     <row r="34">
@@ -2108,7 +2108,7 @@
         <v>1.0</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.8306122448979592</v>
+        <v>0.6853810912119951</v>
       </c>
     </row>
   </sheetData>
